--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-statut.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-statut.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4022" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4022" uniqueCount="385">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -833,6 +833,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7481,7 +7485,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7489,10 +7493,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7518,10 +7522,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7552,7 +7556,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7570,7 +7574,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7590,10 +7594,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7691,10 +7695,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7735,7 +7739,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7794,10 +7798,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7897,10 +7901,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8000,10 +8004,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8103,10 +8107,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8206,10 +8210,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8307,10 +8311,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8408,10 +8412,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8511,10 +8515,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8614,10 +8618,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8717,10 +8721,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8743,13 +8747,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8800,7 +8804,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8820,10 +8824,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8846,7 +8850,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8879,7 +8883,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8897,7 +8901,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8917,10 +8921,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8943,7 +8947,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8996,7 +9000,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9016,10 +9020,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9075,25 +9079,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9113,10 +9117,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9142,7 +9146,7 @@
         <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -9194,7 +9198,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9214,10 +9218,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9315,10 +9319,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9418,10 +9422,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9521,10 +9525,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9624,10 +9628,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9727,10 +9731,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9830,10 +9834,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9931,10 +9935,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10032,10 +10036,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10135,10 +10139,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10166,7 +10170,7 @@
         <v>214</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M85" t="s" s="2">
         <v>215</v>
@@ -10240,10 +10244,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10341,17 +10345,17 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>80</v>
@@ -10369,11 +10373,11 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10424,7 +10428,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10444,10 +10448,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10472,11 +10476,11 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10527,7 +10531,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10547,10 +10551,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10648,10 +10652,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10692,7 +10696,7 @@
         <v>74</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>74</v>
@@ -10751,10 +10755,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10795,7 +10799,7 @@
         <v>74</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>74</v>
@@ -10854,10 +10858,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10898,7 +10902,7 @@
         <v>74</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>74</v>
@@ -10957,10 +10961,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11060,10 +11064,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11104,7 +11108,7 @@
         <v>74</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>74</v>
@@ -11163,10 +11167,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11264,10 +11268,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11365,10 +11369,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11468,10 +11472,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11571,10 +11575,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11674,10 +11678,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11705,10 +11709,10 @@
         <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11759,7 +11763,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11779,10 +11783,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11882,10 +11886,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11908,13 +11912,13 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11945,7 +11949,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>74</v>
@@ -11963,7 +11967,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11983,10 +11987,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12009,7 +12013,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12042,25 +12046,25 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12080,10 +12084,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12110,7 +12114,7 @@
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12161,7 +12165,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12181,10 +12185,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12207,7 +12211,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12260,7 +12264,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12280,10 +12284,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12306,7 +12310,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12359,7 +12363,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12379,10 +12383,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12405,7 +12409,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12458,7 +12462,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12478,10 +12482,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12504,13 +12508,13 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12561,7 +12565,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12581,10 +12585,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12607,7 +12611,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12660,7 +12664,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12680,10 +12684,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12706,7 +12710,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12759,7 +12763,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12779,10 +12783,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12805,7 +12809,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12858,7 +12862,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12878,10 +12882,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12904,7 +12908,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12957,7 +12961,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12977,10 +12981,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13003,7 +13007,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13056,7 +13060,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13076,10 +13080,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13102,7 +13106,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13155,7 +13159,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13175,10 +13179,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13201,11 +13205,11 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13256,7 +13260,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13276,10 +13280,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13377,10 +13381,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13478,10 +13482,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13579,10 +13583,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13680,10 +13684,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13783,10 +13787,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13886,10 +13890,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13989,10 +13993,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14092,10 +14096,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14193,10 +14197,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14230,7 +14234,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>74</v>
@@ -14252,7 +14256,7 @@
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>74</v>
@@ -14270,7 +14274,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14290,10 +14294,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14316,7 +14320,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14369,7 +14373,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
@@ -14389,10 +14393,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14415,7 +14419,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14468,7 +14472,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
